--- a/combine_harvest_abstract/deliverables/Combine_Harvest_Finish_Reconciliation.xlsx
+++ b/combine_harvest_abstract/deliverables/Combine_Harvest_Finish_Reconciliation.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counts" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blank cells filled" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Format parity" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open items" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Verified inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Counts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Blank cells filled" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Format parity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open items" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Counts'!$A$1:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blank cells filled'!$A$1:$F$1310</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Format parity'!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open items'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Counts'!$A$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blank cells filled'!$A$1:$F$1310</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Format parity'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Open items'!$A$1:$C$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,13 +40,39 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -74,9 +101,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -442,6 +481,1490 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Combine-Harvest verified inventory — opened and counted October 15, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>County and federal index rows were counted from the files in this package. Image and page counts are the October 13 instrument-file census (Combine_Harvest_Image_File_and_Tract_Row_Accounting) and the portfolio PDF/raster census. They are not a new walk of every Drive folder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>COUNTY INDEXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Spreadsheet</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Rows through last entry</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Header row</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Data rows from row 10</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Unknown cells in A-H</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Blank A-H cells</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>6-47N-76W</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>47N-76W-6 county index</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Qualified unsigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>7-47N-76W</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>47N-76W-7 county index</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Qualified unsigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>13-47N-77W</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>47N-77W-13 county index</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Qualified unsigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>18-47N-76W</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>47N-76W-18 county index</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Qualified unsigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>19-47N-76W</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>47N-76W-19 county index</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Qualified partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>24-47N-77W</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>47N-77W-24 county index</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>355</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Qualified unsigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>30-47N-76W</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>47N-76W-30 county index</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Qualified partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>31-47N-76W</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>47N-76W-31 county index</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Qualified partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="n">
+        <v>1043</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>BLM / FEDERAL CASE FILES IN THE PACKAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>BLM or federal file</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Rows through last entry</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Documents (data rows)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Parts</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Part split</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Different document types</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Unknown A-H cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>W-40637</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Unknown: 1</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>WYW-094604</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Unknown: 2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>WYW-094605</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1: 64; 2: 37; 3: 20; 4: 1</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>WYW-153528</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1: 90; SRP: 1</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>WYW-153681</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1: 37; 2: 27; SRP: 1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>WYW-133620</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1: 52; 2: 51; 3: 63; 4: 1; SRP: 1</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>WYW-094604</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Unknown: 1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>WYW-094605</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1: 20; 2: 3; 3: 12; County copy: 6</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>WYW-145618</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>County copy: 3; 1: 2</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>WYW-153681</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1: 37; 2: 27; SRP: 1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>WYW-131225</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1: 47; 2: 53; 3: 41; 4: 1; SRP: 1</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>No BLM file in this package</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>No BLM file in this package</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>No BLM file in this package</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>No BLM file in this package</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>BLM TOTAL</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>704</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="n">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>INSTRUMENT IMAGE FILES — October 13 census, not loose PNG folders</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Instrument PDF files</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Pages (images inside those PDFs)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Tract-index pages</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Matched to the index then on file</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Images not on the index then on file</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Placed index rows on Oct 13</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>County data rows now</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>7540</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>9081</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>8980</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>2885</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>9568</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>not in that census</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>not in that census</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>not in that census</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>PDF AND RASTER CENSUS — do not add the section totals; files are shared</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Local file paths</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Directories</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Source PDF paths</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Physical source pages</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Raster placements</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Standalone image files</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>1355</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>7547</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>10901</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2428</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>9092</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>12459</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>1717</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>8997</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>10765</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1734</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>9589</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>12382</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Shared union, not a sum</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>11023 paths / 1330 directories</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>917 source PDF paths / 663 distinct PDF bodies</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>14614</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>18753</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>57 standalone paths / 53 distinct images</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>CHECKLISTS AND LETTERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Each of the 8 section folders has one checklist (9 spreadsheet rows, 6 used, 11 columns, Calibri 11, every label and value filled) and one unsigned certification letter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Sections 19, 30, and 31 index dates now display M/D/YYYY, the same format as the checklists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>STILL OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>What is left</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Signature and release</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Letters are unsigned. This is not a title opinion and not a client release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Sections 19, 30, 31</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Partial. Only rows with authenticated originals. No official starting date or posted-through date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Section 30 holds</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>142117, 174634, and 309041 are unapplied. 169051 is on hold because the images stop at folio 362.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Section 6 BLM</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>No federal case-file index is in the package. The 22 composite source dependencies stay open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Section 7</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Corner Record 161576 is still open. 161575 was not used as a substitute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Sections 13 and 24</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>County acreage 296.600 versus federal 298.600 is unresolved. Original-source joins and the current chain are open. The Oct 13 image match is behind the current row counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Section 18</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>106 instrument images were not on the Oct 13 placed index. Original-source joins remain open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Federal Unknown cells</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1,194 federal A-H cells say Unknown. Those pages were indexed as documents, but the missing fact was not invented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Searches not run</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Judgment, lien, mortgage, and civil-suit searches were not performed. Assessor and treasurer reports are N/A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Machine acceptance</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Windows, live Acrobat, and the PC copy were not accepted in this count.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J10"/>
@@ -821,8 +2344,6 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10">
         <f>SUM(D2:D9)</f>
         <v/>
@@ -846,7 +2367,6 @@
         <f>SUM(I2:I9)</f>
         <v/>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J10"/>
@@ -855,7 +2375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40181,7 +41701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40338,7 +41858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
